--- a/Program_P2_Master_Tracker.xlsx
+++ b/Program_P2_Master_Tracker.xlsx
@@ -22,7 +22,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -33,11 +33,6 @@
     <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="0017365D"/>
-      <sz val="18"/>
     </font>
   </fonts>
   <fills count="3">
@@ -65,15 +60,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -153,12 +147,12 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tracker" displayName="Tracker" ref="A1:M45" headerRowCount="1">
-  <autoFilter ref="A1:M45"/>
-  <tableColumns count="13">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tracker" displayName="Tracker" ref="A1:L45" headerRowCount="1">
+  <autoFilter ref="A1:L45"/>
+  <tableColumns count="12">
     <tableColumn id="1" name="ID"/>
     <tableColumn id="2" name="المؤشر"/>
-    <tableColumn id="3" name="المهمة التشغيلية"/>
+    <tableColumn id="3" name="المهمة"/>
     <tableColumn id="4" name="المسؤول"/>
     <tableColumn id="5" name="المراجع"/>
     <tableColumn id="6" name="جهة الاعتماد"/>
@@ -166,9 +160,8 @@
     <tableColumn id="8" name="الإنجاز %"/>
     <tableColumn id="9" name="الأولوية"/>
     <tableColumn id="10" name="الموعد"/>
-    <tableColumn id="11" name="الدليل المطلوب"/>
-    <tableColumn id="12" name="الفجوة/المتبقي"/>
-    <tableColumn id="13" name="التوافق"/>
+    <tableColumn id="11" name="الدليل"/>
+    <tableColumn id="12" name="الفجوة"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
 </table>
@@ -463,22 +456,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M45"/>
+  <dimension ref="A1:L45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="45" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="42" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="38" customWidth="1" min="11" max="11"/>
+    <col width="40" customWidth="1" min="11" max="11"/>
     <col width="35" customWidth="1" min="12" max="12"/>
-    <col width="16" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -494,7 +486,7 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>المهمة التشغيلية</t>
+          <t>المهمة</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
@@ -534,17 +526,12 @@
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>الدليل المطلوب</t>
+          <t>الدليل</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>الفجوة/المتبقي</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>التوافق</t>
+          <t>الفجوة</t>
         </is>
       </c>
     </row>
@@ -556,22 +543,22 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>P2.1 المعايير الأكاديمية المتبناة</t>
+          <t>P2.1</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>تحديد NARS أو المعايير المرجعية ومصدرها</t>
+          <t>تحديد NARS/ARS ومصدرها</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>عضو فريق P2 رقم 1</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>منسق المعيار ووحدة الجودة</t>
+          <t>منسق المعيار ووحدة ضمان الجودة</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -599,17 +586,12 @@
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>محضر/قرار/وثيقة أو رابط داعم</t>
+          <t>وثيقة تنفيذ، محضر مراجعة، قرار اعتماد، رابط النسخة النهائية</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>استكمال التنفيذ والأدلة</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>غير متحقق</t>
+          <t>استكمال التنفيذ والأدلة والمراجعة والاعتماد والفهرسة.</t>
         </is>
       </c>
     </row>
@@ -621,22 +603,22 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>P2.1 المعايير الأكاديمية المتبناة</t>
+          <t>P2.1</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>تحليل الملاءمة مع طبيعة البرنامج</t>
+          <t>تحليل الملاءمة</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>عضو فريق P2 رقم 2</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>منسق المعيار ووحدة الجودة</t>
+          <t>منسق المعيار ووحدة ضمان الجودة</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -664,17 +646,12 @@
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>محضر/قرار/وثيقة أو رابط داعم</t>
+          <t>وثيقة تنفيذ، محضر مراجعة، قرار اعتماد، رابط النسخة النهائية</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>استكمال التنفيذ والأدلة</t>
-        </is>
-      </c>
-      <c r="M3" s="2" t="inlineStr">
-        <is>
-          <t>غير متحقق</t>
+          <t>استكمال التنفيذ والأدلة والمراجعة والاعتماد والفهرسة.</t>
         </is>
       </c>
     </row>
@@ -686,22 +663,22 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>P2.1 المعايير الأكاديمية المتبناة</t>
+          <t>P2.1</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>إعداد مصفوفة ARS مع NARS عند اللزوم</t>
+          <t>إعداد ARS–NARS Matrix</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>P3</t>
+          <t>عضو فريق P2 رقم 3</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>منسق المعيار ووحدة الجودة</t>
+          <t>منسق المعيار ووحدة ضمان الجودة</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -729,17 +706,12 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>محضر/قرار/وثيقة أو رابط داعم</t>
+          <t>وثيقة تنفيذ، محضر مراجعة، قرار اعتماد، رابط النسخة النهائية</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>استكمال التنفيذ والأدلة</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>غير متحقق</t>
+          <t>استكمال التنفيذ والأدلة والمراجعة والاعتماد والفهرسة.</t>
         </is>
       </c>
     </row>
@@ -751,22 +723,22 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>P2.1 المعايير الأكاديمية المتبناة</t>
+          <t>P2.1</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>عرض ومناقشة المعايير</t>
+          <t>مناقشة المعايير</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>P4</t>
+          <t>عضو فريق P2 رقم 4</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>منسق المعيار ووحدة الجودة</t>
+          <t>منسق المعيار ووحدة ضمان الجودة</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -794,17 +766,12 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>محضر/قرار/وثيقة أو رابط داعم</t>
+          <t>وثيقة تنفيذ، محضر مراجعة، قرار اعتماد، رابط النسخة النهائية</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>استكمال التنفيذ والأدلة</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>غير متحقق</t>
+          <t>استكمال التنفيذ والأدلة والمراجعة والاعتماد والفهرسة.</t>
         </is>
       </c>
     </row>
@@ -816,22 +783,22 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>P2.1 المعايير الأكاديمية المتبناة</t>
+          <t>P2.1</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>اعتماد التبني والتوعية به</t>
+          <t>اعتماد التبني والتوعية</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>عضو فريق P2 رقم 1</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>منسق المعيار ووحدة الجودة</t>
+          <t>منسق المعيار ووحدة ضمان الجودة</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -859,44 +826,39 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>محضر/قرار/وثيقة أو رابط داعم</t>
+          <t>وثيقة تنفيذ، محضر مراجعة، قرار اعتماد، رابط النسخة النهائية</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>استكمال التنفيذ والأدلة</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>غير متحقق</t>
+          <t>استكمال التنفيذ والأدلة والمراجعة والاعتماد والفهرسة.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>P2.2-T06</t>
+          <t>P2.2-T01</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>P2.2 أهداف البرنامج</t>
+          <t>P2.2</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>مراجعة رسالة البرنامج</t>
+          <t>مراجعة الرسالة</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>عضو فريق P2 رقم 2</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>منسق المعيار ووحدة الجودة</t>
+          <t>منسق المعيار ووحدة ضمان الجودة</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -924,29 +886,24 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>محضر/قرار/وثيقة أو رابط داعم</t>
+          <t>وثيقة تنفيذ، محضر مراجعة، قرار اعتماد، رابط النسخة النهائية</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>استكمال التنفيذ والأدلة</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>غير متحقق</t>
+          <t>استكمال التنفيذ والأدلة والمراجعة والاعتماد والفهرسة.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>P2.2-T07</t>
+          <t>P2.2-T02</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>P2.2 أهداف البرنامج</t>
+          <t>P2.2</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -956,12 +913,12 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>عضو فريق P2 رقم 3</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>منسق المعيار ووحدة الجودة</t>
+          <t>منسق المعيار ووحدة ضمان الجودة</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -989,29 +946,24 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>محضر/قرار/وثيقة أو رابط داعم</t>
+          <t>وثيقة تنفيذ، محضر مراجعة، قرار اعتماد، رابط النسخة النهائية</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>استكمال التنفيذ والأدلة</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>غير متحقق</t>
+          <t>استكمال التنفيذ والأدلة والمراجعة والاعتماد والفهرسة.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>P2.2-T08</t>
+          <t>P2.2-T03</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>P2.2 أهداف البرنامج</t>
+          <t>P2.2</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1021,12 +973,12 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>P3</t>
+          <t>عضو فريق P2 رقم 4</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>منسق المعيار ووحدة الجودة</t>
+          <t>منسق المعيار ووحدة ضمان الجودة</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -1054,44 +1006,39 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>محضر/قرار/وثيقة أو رابط داعم</t>
+          <t>وثيقة تنفيذ، محضر مراجعة، قرار اعتماد، رابط النسخة النهائية</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>استكمال التنفيذ والأدلة</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>غير متحقق</t>
+          <t>استكمال التنفيذ والأدلة والمراجعة والاعتماد والفهرسة.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>P2.2-T09</t>
+          <t>P2.2-T04</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>P2.2 أهداف البرنامج</t>
+          <t>P2.2</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>مواءمة الأهداف مع مواصفات الخريج</t>
+          <t>مواءمتها مع مواصفات الخريج</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>P4</t>
+          <t>عضو فريق P2 رقم 1</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>منسق المعيار ووحدة الجودة</t>
+          <t>منسق المعيار ووحدة ضمان الجودة</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -1119,44 +1066,39 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>محضر/قرار/وثيقة أو رابط داعم</t>
+          <t>وثيقة تنفيذ، محضر مراجعة، قرار اعتماد، رابط النسخة النهائية</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>استكمال التنفيذ والأدلة</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>غير متحقق</t>
+          <t>استكمال التنفيذ والأدلة والمراجعة والاعتماد والفهرسة.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>P2.2-T10</t>
+          <t>P2.2-T05</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>P2.2 أهداف البرنامج</t>
+          <t>P2.2</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>اعتماد الأهداف وإعلانها</t>
+          <t>الاعتماد والإعلان</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>عضو فريق P2 رقم 2</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>منسق المعيار ووحدة الجودة</t>
+          <t>منسق المعيار ووحدة ضمان الجودة</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1184,44 +1126,39 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>محضر/قرار/وثيقة أو رابط داعم</t>
+          <t>وثيقة تنفيذ، محضر مراجعة، قرار اعتماد، رابط النسخة النهائية</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>استكمال التنفيذ والأدلة</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>غير متحقق</t>
+          <t>استكمال التنفيذ والأدلة والمراجعة والاعتماد والفهرسة.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>P2.3-T11</t>
+          <t>P2.3-T01</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>P2.3 هيكل البرنامج</t>
+          <t>P2.3</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>تحليل مكونات وساعات البرنامج</t>
+          <t>تحليل الساعات والمكونات</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>عضو فريق P2 رقم 3</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>منسق المعيار ووحدة الجودة</t>
+          <t>منسق المعيار ووحدة ضمان الجودة</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1249,44 +1186,39 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>محضر/قرار/وثيقة أو رابط داعم</t>
+          <t>وثيقة تنفيذ، محضر مراجعة، قرار اعتماد، رابط النسخة النهائية</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>استكمال التنفيذ والأدلة</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>غير متحقق</t>
+          <t>استكمال التنفيذ والأدلة والمراجعة والاعتماد والفهرسة.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>P2.3-T12</t>
+          <t>P2.3-T02</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>P2.3 هيكل البرنامج</t>
+          <t>P2.3</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>تحليل التكامل والتسلسل والمتطلبات السابقة</t>
+          <t>تحليل التكامل والتسلسل</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>عضو فريق P2 رقم 4</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>منسق المعيار ووحدة الجودة</t>
+          <t>منسق المعيار ووحدة ضمان الجودة</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1314,44 +1246,39 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>محضر/قرار/وثيقة أو رابط داعم</t>
+          <t>وثيقة تنفيذ، محضر مراجعة، قرار اعتماد، رابط النسخة النهائية</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>استكمال التنفيذ والأدلة</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>غير متحقق</t>
+          <t>استكمال التنفيذ والأدلة والمراجعة والاعتماد والفهرسة.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>P2.3-T13</t>
+          <t>P2.3-T03</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>P2.3 هيكل البرنامج</t>
+          <t>P2.3</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>تحليل الحداثة العلمية والمهنية</t>
+          <t>تحليل الحداثة</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>P3</t>
+          <t>عضو فريق P2 رقم 1</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>منسق المعيار ووحدة الجودة</t>
+          <t>منسق المعيار ووحدة ضمان الجودة</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1379,29 +1306,24 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>محضر/قرار/وثيقة أو رابط داعم</t>
+          <t>وثيقة تنفيذ، محضر مراجعة، قرار اعتماد، رابط النسخة النهائية</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>استكمال التنفيذ والأدلة</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>غير متحقق</t>
+          <t>استكمال التنفيذ والأدلة والمراجعة والاعتماد والفهرسة.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>P2.3-T14</t>
+          <t>P2.3-T04</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>P2.3 هيكل البرنامج</t>
+          <t>P2.3</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1411,12 +1333,12 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>P4</t>
+          <t>عضو فريق P2 رقم 2</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>منسق المعيار ووحدة الجودة</t>
+          <t>منسق المعيار ووحدة ضمان الجودة</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1444,44 +1366,39 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>محضر/قرار/وثيقة أو رابط داعم</t>
+          <t>وثيقة تنفيذ، محضر مراجعة، قرار اعتماد، رابط النسخة النهائية</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>استكمال التنفيذ والأدلة</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>غير متحقق</t>
+          <t>استكمال التنفيذ والأدلة والمراجعة والاعتماد والفهرسة.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>P2.3-T15</t>
+          <t>P2.3-T05</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>P2.3 هيكل البرنامج</t>
+          <t>P2.3</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>تحليل متطلبات التخصص والمتطلبات العامة</t>
+          <t>تحليل المتطلبات</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>عضو فريق P2 رقم 3</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>منسق المعيار ووحدة الجودة</t>
+          <t>منسق المعيار ووحدة ضمان الجودة</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1509,44 +1426,39 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>محضر/قرار/وثيقة أو رابط داعم</t>
+          <t>وثيقة تنفيذ، محضر مراجعة، قرار اعتماد، رابط النسخة النهائية</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>استكمال التنفيذ والأدلة</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>غير متحقق</t>
+          <t>استكمال التنفيذ والأدلة والمراجعة والاعتماد والفهرسة.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>P2.3-T16</t>
+          <t>P2.3-T06</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>P2.3 هيكل البرنامج</t>
+          <t>P2.3</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>معالجة الفجوات واعتماد التحديثات</t>
+          <t>اعتماد التحديثات</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>عضو فريق P2 رقم 4</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>منسق المعيار ووحدة الجودة</t>
+          <t>منسق المعيار ووحدة ضمان الجودة</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -1574,29 +1486,24 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>محضر/قرار/وثيقة أو رابط داعم</t>
+          <t>وثيقة تنفيذ، محضر مراجعة، قرار اعتماد، رابط النسخة النهائية</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>استكمال التنفيذ والأدلة</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>غير متحقق</t>
+          <t>استكمال التنفيذ والأدلة والمراجعة والاعتماد والفهرسة.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>P2.4-T17</t>
+          <t>P2.4-T01</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>P2.4 استراتيجية التعليم والتعلم والتقييم</t>
+          <t>P2.4</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1606,12 +1513,12 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>عضو فريق P2 رقم 1</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>منسق المعيار ووحدة الجودة</t>
+          <t>منسق المعيار ووحدة ضمان الجودة</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1639,44 +1546,39 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>محضر/قرار/وثيقة أو رابط داعم</t>
+          <t>وثيقة تنفيذ، محضر مراجعة، قرار اعتماد، رابط النسخة النهائية</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>استكمال التنفيذ والأدلة</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>غير متحقق</t>
+          <t>استكمال التنفيذ والأدلة والمراجعة والاعتماد والفهرسة.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>P2.4-T18</t>
+          <t>P2.4-T02</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>P2.4 استراتيجية التعليم والتعلم والتقييم</t>
+          <t>P2.4</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>مواءمتها مع المعايير الأكاديمية</t>
+          <t>مواءمتها مع المعايير</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>عضو فريق P2 رقم 2</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>منسق المعيار ووحدة الجودة</t>
+          <t>منسق المعيار ووحدة ضمان الجودة</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -1704,44 +1606,39 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>محضر/قرار/وثيقة أو رابط داعم</t>
+          <t>وثيقة تنفيذ، محضر مراجعة، قرار اعتماد، رابط النسخة النهائية</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>استكمال التنفيذ والأدلة</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>غير متحقق</t>
+          <t>استكمال التنفيذ والأدلة والمراجعة والاعتماد والفهرسة.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>P2.4-T19</t>
+          <t>P2.4-T03</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>P2.4 استراتيجية التعليم والتعلم والتقييم</t>
+          <t>P2.4</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>ربط طرق التعليم بالمخرجات</t>
+          <t>ربط التعليم بالمخرجات</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>P3</t>
+          <t>عضو فريق P2 رقم 3</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>منسق المعيار ووحدة الجودة</t>
+          <t>منسق المعيار ووحدة ضمان الجودة</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1769,44 +1666,39 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>محضر/قرار/وثيقة أو رابط داعم</t>
+          <t>وثيقة تنفيذ، محضر مراجعة، قرار اعتماد، رابط النسخة النهائية</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>استكمال التنفيذ والأدلة</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>غير متحقق</t>
+          <t>استكمال التنفيذ والأدلة والمراجعة والاعتماد والفهرسة.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>P2.4-T20</t>
+          <t>P2.4-T04</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>P2.4 استراتيجية التعليم والتعلم والتقييم</t>
+          <t>P2.4</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>ربط طرق التقييم بالمخرجات</t>
+          <t>ربط التقييم بالمخرجات</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>P4</t>
+          <t>عضو فريق P2 رقم 4</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>منسق المعيار ووحدة الجودة</t>
+          <t>منسق المعيار ووحدة ضمان الجودة</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -1834,44 +1726,39 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>محضر/قرار/وثيقة أو رابط داعم</t>
+          <t>وثيقة تنفيذ، محضر مراجعة، قرار اعتماد، رابط النسخة النهائية</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>استكمال التنفيذ والأدلة</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>غير متحقق</t>
+          <t>استكمال التنفيذ والأدلة والمراجعة والاعتماد والفهرسة.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>P2.4-T21</t>
+          <t>P2.4-T05</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>P2.4 استراتيجية التعليم والتعلم والتقييم</t>
+          <t>P2.4</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>اعتماد الاستراتيجية وإعلانها</t>
+          <t>الاعتماد والإعلان</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>عضو فريق P2 رقم 1</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>منسق المعيار ووحدة الجودة</t>
+          <t>منسق المعيار ووحدة ضمان الجودة</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1899,44 +1786,39 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>محضر/قرار/وثيقة أو رابط داعم</t>
+          <t>وثيقة تنفيذ، محضر مراجعة، قرار اعتماد، رابط النسخة النهائية</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>استكمال التنفيذ والأدلة</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>غير متحقق</t>
+          <t>استكمال التنفيذ والأدلة والمراجعة والاعتماد والفهرسة.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>P2.4-T22</t>
+          <t>P2.4-T06</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>P2.4 استراتيجية التعليم والتعلم والتقييم</t>
+          <t>P2.4</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>المراجعة الدورية والتحديث</t>
+          <t>المراجعة الدورية</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>عضو فريق P2 رقم 2</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>منسق المعيار ووحدة الجودة</t>
+          <t>منسق المعيار ووحدة ضمان الجودة</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -1964,44 +1846,39 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>محضر/قرار/وثيقة أو رابط داعم</t>
+          <t>وثيقة تنفيذ، محضر مراجعة، قرار اعتماد، رابط النسخة النهائية</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>استكمال التنفيذ والأدلة</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>غير متحقق</t>
+          <t>استكمال التنفيذ والأدلة والمراجعة والاعتماد والفهرسة.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>P2.5-T23</t>
+          <t>P2.5-T01</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>P2.5 توصيف البرنامج</t>
+          <t>P2.5</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>استكمال نموذج توصيف البرنامج الساري</t>
+          <t>استكمال نموذج التوصيف</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>عضو فريق P2 رقم 3</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>منسق المعيار ووحدة الجودة</t>
+          <t>منسق المعيار ووحدة ضمان الجودة</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -2029,44 +1906,39 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>محضر/قرار/وثيقة أو رابط داعم</t>
+          <t>وثيقة تنفيذ، محضر مراجعة، قرار اعتماد، رابط النسخة النهائية</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>استكمال التنفيذ والأدلة</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>غير متحقق</t>
+          <t>استكمال التنفيذ والأدلة والمراجعة والاعتماد والفهرسة.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>P2.5-T24</t>
+          <t>P2.5-T02</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>P2.5 توصيف البرنامج</t>
+          <t>P2.5</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>مطابقة التوصيف مع اللائحة</t>
+          <t>مطابقة اللائحة</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>عضو فريق P2 رقم 4</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>منسق المعيار ووحدة الجودة</t>
+          <t>منسق المعيار ووحدة ضمان الجودة</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -2094,44 +1966,39 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>محضر/قرار/وثيقة أو رابط داعم</t>
+          <t>وثيقة تنفيذ، محضر مراجعة، قرار اعتماد، رابط النسخة النهائية</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>استكمال التنفيذ والأدلة</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>غير متحقق</t>
+          <t>استكمال التنفيذ والأدلة والمراجعة والاعتماد والفهرسة.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>P2.5-T25</t>
+          <t>P2.5-T03</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>P2.5 توصيف البرنامج</t>
+          <t>P2.5</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>مراجعة البيانات والأهداف والهيكل</t>
+          <t>مراجعة البيانات والهيكل</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>P3</t>
+          <t>عضو فريق P2 رقم 1</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>منسق المعيار ووحدة الجودة</t>
+          <t>منسق المعيار ووحدة ضمان الجودة</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -2159,29 +2026,24 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>محضر/قرار/وثيقة أو رابط داعم</t>
+          <t>وثيقة تنفيذ، محضر مراجعة، قرار اعتماد، رابط النسخة النهائية</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>استكمال التنفيذ والأدلة</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>غير متحقق</t>
+          <t>استكمال التنفيذ والأدلة والمراجعة والاعتماد والفهرسة.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>P2.5-T26</t>
+          <t>P2.5-T04</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>P2.5 توصيف البرنامج</t>
+          <t>P2.5</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2191,12 +2053,12 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>P4</t>
+          <t>عضو فريق P2 رقم 2</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>منسق المعيار ووحدة الجودة</t>
+          <t>منسق المعيار ووحدة ضمان الجودة</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -2224,44 +2086,39 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>محضر/قرار/وثيقة أو رابط داعم</t>
+          <t>وثيقة تنفيذ، محضر مراجعة، قرار اعتماد، رابط النسخة النهائية</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>استكمال التنفيذ والأدلة</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t>غير متحقق</t>
+          <t>استكمال التنفيذ والأدلة والمراجعة والاعتماد والفهرسة.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>P2.5-T27</t>
+          <t>P2.5-T05</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>P2.5 توصيف البرنامج</t>
+          <t>P2.5</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>إعلان التوصيف وإتاحته</t>
+          <t>إعلانه وإتاحته</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>عضو فريق P2 رقم 3</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>منسق المعيار ووحدة الجودة</t>
+          <t>منسق المعيار ووحدة ضمان الجودة</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -2289,44 +2146,39 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>محضر/قرار/وثيقة أو رابط داعم</t>
+          <t>وثيقة تنفيذ، محضر مراجعة، قرار اعتماد، رابط النسخة النهائية</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>استكمال التنفيذ والأدلة</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr">
-        <is>
-          <t>غير متحقق</t>
+          <t>استكمال التنفيذ والأدلة والمراجعة والاعتماد والفهرسة.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>P2.6-T28</t>
+          <t>P2.6-T01</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>P2.6 مصفوفات الاتساق</t>
+          <t>P2.6</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>إعداد مصفوفة PLO مع المعايير</t>
+          <t>PLO–Standards Matrix</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>عضو فريق P2 رقم 4</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>منسق المعيار ووحدة الجودة</t>
+          <t>منسق المعيار ووحدة ضمان الجودة</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -2354,44 +2206,39 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>محضر/قرار/وثيقة أو رابط داعم</t>
+          <t>وثيقة تنفيذ، محضر مراجعة، قرار اعتماد، رابط النسخة النهائية</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>استكمال التنفيذ والأدلة</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr">
-        <is>
-          <t>غير متحقق</t>
+          <t>استكمال التنفيذ والأدلة والمراجعة والاعتماد والفهرسة.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>P2.6-T29</t>
+          <t>P2.6-T02</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>P2.6 مصفوفات الاتساق</t>
+          <t>P2.6</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>إعداد مصفوفة PLO مع المقررات الإجبارية</t>
+          <t>PLO–Courses Matrix</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>عضو فريق P2 رقم 1</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>منسق المعيار ووحدة الجودة</t>
+          <t>منسق المعيار ووحدة ضمان الجودة</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2419,44 +2266,39 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>محضر/قرار/وثيقة أو رابط داعم</t>
+          <t>وثيقة تنفيذ، محضر مراجعة، قرار اعتماد، رابط النسخة النهائية</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>استكمال التنفيذ والأدلة</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="inlineStr">
-        <is>
-          <t>غير متحقق</t>
+          <t>استكمال التنفيذ والأدلة والمراجعة والاعتماد والفهرسة.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>P2.6-T30</t>
+          <t>P2.6-T03</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>P2.6 مصفوفات الاتساق</t>
+          <t>P2.6</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>إعداد مصفوفة المقررات الاختيارية</t>
+          <t>مصفوفة الاختياري</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>P3</t>
+          <t>عضو فريق P2 رقم 2</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>منسق المعيار ووحدة الجودة</t>
+          <t>منسق المعيار ووحدة ضمان الجودة</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -2484,44 +2326,39 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>محضر/قرار/وثيقة أو رابط داعم</t>
+          <t>وثيقة تنفيذ، محضر مراجعة، قرار اعتماد، رابط النسخة النهائية</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>استكمال التنفيذ والأدلة</t>
-        </is>
-      </c>
-      <c r="M31" s="2" t="inlineStr">
-        <is>
-          <t>غير متحقق</t>
+          <t>استكمال التنفيذ والأدلة والمراجعة والاعتماد والفهرسة.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>P2.6-T31</t>
+          <t>P2.6-T04</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>P2.6 مصفوفات الاتساق</t>
+          <t>P2.6</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>إعداد مصفوفة طرق التعليم والتعلم</t>
+          <t>مصفوفة التعليم</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>P4</t>
+          <t>عضو فريق P2 رقم 3</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>منسق المعيار ووحدة الجودة</t>
+          <t>منسق المعيار ووحدة ضمان الجودة</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2549,44 +2386,39 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>محضر/قرار/وثيقة أو رابط داعم</t>
+          <t>وثيقة تنفيذ، محضر مراجعة، قرار اعتماد، رابط النسخة النهائية</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>استكمال التنفيذ والأدلة</t>
-        </is>
-      </c>
-      <c r="M32" s="2" t="inlineStr">
-        <is>
-          <t>غير متحقق</t>
+          <t>استكمال التنفيذ والأدلة والمراجعة والاعتماد والفهرسة.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>P2.6-T32</t>
+          <t>P2.6-T05</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>P2.6 مصفوفات الاتساق</t>
+          <t>P2.6</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>إعداد مصفوفة طرق التقييم</t>
+          <t>مصفوفة التقييم</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>عضو فريق P2 رقم 4</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>منسق المعيار ووحدة الجودة</t>
+          <t>منسق المعيار ووحدة ضمان الجودة</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
@@ -2614,44 +2446,39 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>محضر/قرار/وثيقة أو رابط داعم</t>
+          <t>وثيقة تنفيذ، محضر مراجعة، قرار اعتماد، رابط النسخة النهائية</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>استكمال التنفيذ والأدلة</t>
-        </is>
-      </c>
-      <c r="M33" s="2" t="inlineStr">
-        <is>
-          <t>غير متحقق</t>
+          <t>استكمال التنفيذ والأدلة والمراجعة والاعتماد والفهرسة.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>P2.6-T33</t>
+          <t>P2.6-T06</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>P2.6 مصفوفات الاتساق</t>
+          <t>P2.6</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>تحليل الفجوات والتكرار واعتماد المعالجة</t>
+          <t>تحليل الفجوات</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>عضو فريق P2 رقم 1</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>منسق المعيار ووحدة الجودة</t>
+          <t>منسق المعيار ووحدة ضمان الجودة</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2679,44 +2506,39 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>محضر/قرار/وثيقة أو رابط داعم</t>
+          <t>وثيقة تنفيذ، محضر مراجعة، قرار اعتماد، رابط النسخة النهائية</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>استكمال التنفيذ والأدلة</t>
-        </is>
-      </c>
-      <c r="M34" s="2" t="inlineStr">
-        <is>
-          <t>غير متحقق</t>
+          <t>استكمال التنفيذ والأدلة والمراجعة والاعتماد والفهرسة.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>P2.7-T34</t>
+          <t>P2.7-T01</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>P2.7 توصيفات المقررات</t>
+          <t>P2.7</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>حصر جميع المقررات وحالة التوصيف</t>
+          <t>حصر المقررات</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>عضو فريق P2 رقم 2</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>منسق المعيار ووحدة الجودة</t>
+          <t>منسق المعيار ووحدة ضمان الجودة</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
@@ -2744,44 +2566,39 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>محضر/قرار/وثيقة أو رابط داعم</t>
+          <t>وثيقة تنفيذ، محضر مراجعة، قرار اعتماد، رابط النسخة النهائية</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>استكمال التنفيذ والأدلة</t>
-        </is>
-      </c>
-      <c r="M35" s="2" t="inlineStr">
-        <is>
-          <t>غير متحقق</t>
+          <t>استكمال التنفيذ والأدلة والمراجعة والاعتماد والفهرسة.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>P2.7-T35</t>
+          <t>P2.7-T02</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>P2.7 توصيفات المقررات</t>
+          <t>P2.7</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>استكمال توصيف كل مقرر</t>
+          <t>استكمال التوصيفات</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>عضو فريق P2 رقم 3</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>منسق المعيار ووحدة الجودة</t>
+          <t>منسق المعيار ووحدة ضمان الجودة</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -2809,44 +2626,39 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>محضر/قرار/وثيقة أو رابط داعم</t>
+          <t>وثيقة تنفيذ، محضر مراجعة، قرار اعتماد، رابط النسخة النهائية</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>استكمال التنفيذ والأدلة</t>
-        </is>
-      </c>
-      <c r="M36" s="2" t="inlineStr">
-        <is>
-          <t>غير متحقق</t>
+          <t>استكمال التنفيذ والأدلة والمراجعة والاعتماد والفهرسة.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>P2.7-T36</t>
+          <t>P2.7-T03</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>P2.7 توصيفات المقررات</t>
+          <t>P2.7</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>مطابقة التوصيفات مع اللائحة</t>
+          <t>مطابقة اللائحة</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>P3</t>
+          <t>عضو فريق P2 رقم 4</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>منسق المعيار ووحدة الجودة</t>
+          <t>منسق المعيار ووحدة ضمان الجودة</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
@@ -2874,44 +2686,39 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>محضر/قرار/وثيقة أو رابط داعم</t>
+          <t>وثيقة تنفيذ، محضر مراجعة، قرار اعتماد، رابط النسخة النهائية</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>استكمال التنفيذ والأدلة</t>
-        </is>
-      </c>
-      <c r="M37" s="2" t="inlineStr">
-        <is>
-          <t>غير متحقق</t>
+          <t>استكمال التنفيذ والأدلة والمراجعة والاعتماد والفهرسة.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>P2.7-T37</t>
+          <t>P2.7-T04</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>P2.7 توصيفات المقررات</t>
+          <t>P2.7</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>مراجعة النواتج وطرق التعليم والتقييم</t>
+          <t>مراجعة النواتج والتقييم</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>P4</t>
+          <t>عضو فريق P2 رقم 1</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>منسق المعيار ووحدة الجودة</t>
+          <t>منسق المعيار ووحدة ضمان الجودة</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -2939,44 +2746,39 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>محضر/قرار/وثيقة أو رابط داعم</t>
+          <t>وثيقة تنفيذ، محضر مراجعة، قرار اعتماد، رابط النسخة النهائية</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>استكمال التنفيذ والأدلة</t>
-        </is>
-      </c>
-      <c r="M38" s="2" t="inlineStr">
-        <is>
-          <t>غير متحقق</t>
+          <t>استكمال التنفيذ والأدلة والمراجعة والاعتماد والفهرسة.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>P2.7-T38</t>
+          <t>P2.7-T05</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>P2.7 توصيفات المقررات</t>
+          <t>P2.7</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>اعتماد التوصيفات وإعلانها</t>
+          <t>الاعتماد والإعلان</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>عضو فريق P2 رقم 2</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>منسق المعيار ووحدة الجودة</t>
+          <t>منسق المعيار ووحدة ضمان الجودة</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
@@ -3004,44 +2806,39 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>محضر/قرار/وثيقة أو رابط داعم</t>
+          <t>وثيقة تنفيذ، محضر مراجعة، قرار اعتماد، رابط النسخة النهائية</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>استكمال التنفيذ والأدلة</t>
-        </is>
-      </c>
-      <c r="M39" s="2" t="inlineStr">
-        <is>
-          <t>غير متحقق</t>
+          <t>استكمال التنفيذ والأدلة والمراجعة والاعتماد والفهرسة.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>P2.8-T39</t>
+          <t>P2.8-T01</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>P2.8 مشاركة الأطراف المعنية في التطوير</t>
+          <t>P2.8</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>تحديد الأطراف المعنية وآلية المشاركة</t>
+          <t>تحديد الأطراف</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>عضو فريق P2 رقم 3</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>منسق المعيار ووحدة الجودة</t>
+          <t>منسق المعيار ووحدة ضمان الجودة</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
@@ -3069,44 +2866,39 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>محضر/قرار/وثيقة أو رابط داعم</t>
+          <t>وثيقة تنفيذ، محضر مراجعة، قرار اعتماد، رابط النسخة النهائية</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>استكمال التنفيذ والأدلة</t>
-        </is>
-      </c>
-      <c r="M40" s="2" t="inlineStr">
-        <is>
-          <t>غير متحقق</t>
+          <t>استكمال التنفيذ والأدلة والمراجعة والاعتماد والفهرسة.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>P2.8-T40</t>
+          <t>P2.8-T02</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>P2.8 مشاركة الأطراف المعنية في التطوير</t>
+          <t>P2.8</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>جمع وتحليل آراء الطلاب والخريجين</t>
+          <t>تحليل آراء الطلاب والخريجين</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>عضو فريق P2 رقم 4</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>منسق المعيار ووحدة الجودة</t>
+          <t>منسق المعيار ووحدة ضمان الجودة</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
@@ -3134,44 +2926,39 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>محضر/قرار/وثيقة أو رابط داعم</t>
+          <t>وثيقة تنفيذ، محضر مراجعة، قرار اعتماد، رابط النسخة النهائية</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>استكمال التنفيذ والأدلة</t>
-        </is>
-      </c>
-      <c r="M41" s="2" t="inlineStr">
-        <is>
-          <t>غير متحقق</t>
+          <t>استكمال التنفيذ والأدلة والمراجعة والاعتماد والفهرسة.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>P2.8-T41</t>
+          <t>P2.8-T03</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>P2.8 مشاركة الأطراف المعنية في التطوير</t>
+          <t>P2.8</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>جمع وتحليل آراء جهات التوظيف</t>
+          <t>تحليل جهات التوظيف</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>P3</t>
+          <t>عضو فريق P2 رقم 1</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>منسق المعيار ووحدة الجودة</t>
+          <t>منسق المعيار ووحدة ضمان الجودة</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
@@ -3199,44 +2986,39 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>محضر/قرار/وثيقة أو رابط داعم</t>
+          <t>وثيقة تنفيذ، محضر مراجعة، قرار اعتماد، رابط النسخة النهائية</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>استكمال التنفيذ والأدلة</t>
-        </is>
-      </c>
-      <c r="M42" s="2" t="inlineStr">
-        <is>
-          <t>غير متحقق</t>
+          <t>استكمال التنفيذ والأدلة والمراجعة والاعتماد والفهرسة.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>P2.8-T42</t>
+          <t>P2.8-T04</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>P2.8 مشاركة الأطراف المعنية في التطوير</t>
+          <t>P2.8</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>مناقشة نتائج التقييم المستمر</t>
+          <t>مناقشة التقييم المستمر</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>P4</t>
+          <t>عضو فريق P2 رقم 2</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>منسق المعيار ووحدة الجودة</t>
+          <t>منسق المعيار ووحدة ضمان الجودة</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
@@ -3264,44 +3046,39 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>محضر/قرار/وثيقة أو رابط داعم</t>
+          <t>وثيقة تنفيذ، محضر مراجعة، قرار اعتماد، رابط النسخة النهائية</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>استكمال التنفيذ والأدلة</t>
-        </is>
-      </c>
-      <c r="M43" s="2" t="inlineStr">
-        <is>
-          <t>غير متحقق</t>
+          <t>استكمال التنفيذ والأدلة والمراجعة والاعتماد والفهرسة.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>P2.8-T43</t>
+          <t>P2.8-T05</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>P2.8 مشاركة الأطراف المعنية في التطوير</t>
+          <t>P2.8</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>إعداد واعتماد إجراءات التطوير</t>
+          <t>اعتماد التطوير</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>عضو فريق P2 رقم 3</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>منسق المعيار ووحدة الجودة</t>
+          <t>منسق المعيار ووحدة ضمان الجودة</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
@@ -3329,44 +3106,39 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>محضر/قرار/وثيقة أو رابط داعم</t>
+          <t>وثيقة تنفيذ، محضر مراجعة، قرار اعتماد، رابط النسخة النهائية</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>استكمال التنفيذ والأدلة</t>
-        </is>
-      </c>
-      <c r="M44" s="2" t="inlineStr">
-        <is>
-          <t>غير متحقق</t>
+          <t>استكمال التنفيذ والأدلة والمراجعة والاعتماد والفهرسة.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>P2.8-T44</t>
+          <t>P2.8-T06</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>P2.8 مشاركة الأطراف المعنية في التطوير</t>
+          <t>P2.8</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>متابعة تنفيذ التطوير وقياس أثره</t>
+          <t>قياس الأثر</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>عضو فريق P2 رقم 4</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>منسق المعيار ووحدة الجودة</t>
+          <t>منسق المعيار ووحدة ضمان الجودة</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
@@ -3394,17 +3166,12 @@
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>محضر/قرار/وثيقة أو رابط داعم</t>
+          <t>وثيقة تنفيذ، محضر مراجعة، قرار اعتماد، رابط النسخة النهائية</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>استكمال التنفيذ والأدلة</t>
-        </is>
-      </c>
-      <c r="M45" s="2" t="inlineStr">
-        <is>
-          <t>غير متحقق</t>
+          <t>استكمال التنفيذ والأدلة والمراجعة والاعتماد والفهرسة.</t>
         </is>
       </c>
     </row>
@@ -3422,155 +3189,143 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="48" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>المعيار الثاني البرامجي P2</t>
-        </is>
+          <t>المؤشر</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>عدد المهام</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>متوسط الإنجاز</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>P2.1</t>
+        </is>
+      </c>
+      <c r="B2">
+        <f>COUNTIF('Master Tracker'!B:B,"P2.1")</f>
+        <v/>
+      </c>
+      <c r="C2" s="4">
+        <f>IFERROR(AVERAGEIF('Master Tracker'!B:B,"P2.1",'Master Tracker'!H:H),0)</f>
+        <v/>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>المؤشر</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>عدد المهام</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>متوسط الإنجاز</t>
-        </is>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>P2.2</t>
+        </is>
+      </c>
+      <c r="B3">
+        <f>COUNTIF('Master Tracker'!B:B,"P2.2")</f>
+        <v/>
+      </c>
+      <c r="C3" s="4">
+        <f>IFERROR(AVERAGEIF('Master Tracker'!B:B,"P2.2",'Master Tracker'!H:H),0)</f>
+        <v/>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>P2.1 المعايير الأكاديمية المتبناة</t>
+          <t>P2.3</t>
         </is>
       </c>
       <c r="B4">
-        <f>COUNTIF('Master Tracker'!B:B,"P2.1*")</f>
+        <f>COUNTIF('Master Tracker'!B:B,"P2.3")</f>
         <v/>
       </c>
-      <c r="C4" s="5">
-        <f>IFERROR(AVERAGEIF('Master Tracker'!B:B,"P2.1*",'Master Tracker'!H:H),0)</f>
+      <c r="C4" s="4">
+        <f>IFERROR(AVERAGEIF('Master Tracker'!B:B,"P2.3",'Master Tracker'!H:H),0)</f>
         <v/>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>P2.2 أهداف البرنامج</t>
+          <t>P2.4</t>
         </is>
       </c>
       <c r="B5">
-        <f>COUNTIF('Master Tracker'!B:B,"P2.2*")</f>
+        <f>COUNTIF('Master Tracker'!B:B,"P2.4")</f>
         <v/>
       </c>
-      <c r="C5" s="5">
-        <f>IFERROR(AVERAGEIF('Master Tracker'!B:B,"P2.2*",'Master Tracker'!H:H),0)</f>
+      <c r="C5" s="4">
+        <f>IFERROR(AVERAGEIF('Master Tracker'!B:B,"P2.4",'Master Tracker'!H:H),0)</f>
         <v/>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>P2.3 هيكل البرنامج</t>
+          <t>P2.5</t>
         </is>
       </c>
       <c r="B6">
-        <f>COUNTIF('Master Tracker'!B:B,"P2.3*")</f>
+        <f>COUNTIF('Master Tracker'!B:B,"P2.5")</f>
         <v/>
       </c>
-      <c r="C6" s="5">
-        <f>IFERROR(AVERAGEIF('Master Tracker'!B:B,"P2.3*",'Master Tracker'!H:H),0)</f>
+      <c r="C6" s="4">
+        <f>IFERROR(AVERAGEIF('Master Tracker'!B:B,"P2.5",'Master Tracker'!H:H),0)</f>
         <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>P2.4 استراتيجية التعليم والتعلم والتقييم</t>
+          <t>P2.6</t>
         </is>
       </c>
       <c r="B7">
-        <f>COUNTIF('Master Tracker'!B:B,"P2.4*")</f>
+        <f>COUNTIF('Master Tracker'!B:B,"P2.6")</f>
         <v/>
       </c>
-      <c r="C7" s="5">
-        <f>IFERROR(AVERAGEIF('Master Tracker'!B:B,"P2.4*",'Master Tracker'!H:H),0)</f>
+      <c r="C7" s="4">
+        <f>IFERROR(AVERAGEIF('Master Tracker'!B:B,"P2.6",'Master Tracker'!H:H),0)</f>
         <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>P2.5 توصيف البرنامج</t>
+          <t>P2.7</t>
         </is>
       </c>
       <c r="B8">
-        <f>COUNTIF('Master Tracker'!B:B,"P2.5*")</f>
+        <f>COUNTIF('Master Tracker'!B:B,"P2.7")</f>
         <v/>
       </c>
-      <c r="C8" s="5">
-        <f>IFERROR(AVERAGEIF('Master Tracker'!B:B,"P2.5*",'Master Tracker'!H:H),0)</f>
+      <c r="C8" s="4">
+        <f>IFERROR(AVERAGEIF('Master Tracker'!B:B,"P2.7",'Master Tracker'!H:H),0)</f>
         <v/>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>P2.6 مصفوفات الاتساق</t>
+          <t>P2.8</t>
         </is>
       </c>
       <c r="B9">
-        <f>COUNTIF('Master Tracker'!B:B,"P2.6*")</f>
+        <f>COUNTIF('Master Tracker'!B:B,"P2.8")</f>
         <v/>
       </c>
-      <c r="C9" s="5">
-        <f>IFERROR(AVERAGEIF('Master Tracker'!B:B,"P2.6*",'Master Tracker'!H:H),0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>P2.7 توصيفات المقررات</t>
-        </is>
-      </c>
-      <c r="B10">
-        <f>COUNTIF('Master Tracker'!B:B,"P2.7*")</f>
-        <v/>
-      </c>
-      <c r="C10" s="5">
-        <f>IFERROR(AVERAGEIF('Master Tracker'!B:B,"P2.7*",'Master Tracker'!H:H),0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>P2.8 مشاركة الأطراف المعنية في التطوير</t>
-        </is>
-      </c>
-      <c r="B11">
-        <f>COUNTIF('Master Tracker'!B:B,"P2.8*")</f>
-        <v/>
-      </c>
-      <c r="C11" s="5">
-        <f>IFERROR(AVERAGEIF('Master Tracker'!B:B,"P2.8*",'Master Tracker'!H:H),0)</f>
+      <c r="C9" s="4">
+        <f>IFERROR(AVERAGEIF('Master Tracker'!B:B,"P2.8",'Master Tracker'!H:H),0)</f>
         <v/>
       </c>
     </row>
@@ -3585,43 +3340,33 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:E1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>الكود</t>
         </is>
       </c>
-      <c r="B1" s="4" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>Task ID</t>
         </is>
       </c>
-      <c r="C1" s="4" t="inlineStr">
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>الدليل</t>
         </is>
       </c>
-      <c r="D1" s="4" t="inlineStr">
+      <c r="D1" s="3" t="inlineStr">
         <is>
           <t>الحالة</t>
         </is>
       </c>
-      <c r="E1" s="4" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>الرابط</t>
-        </is>
-      </c>
-      <c r="F1" s="4" t="inlineStr">
-        <is>
-          <t>المراجع</t>
-        </is>
-      </c>
-      <c r="G1" s="4" t="inlineStr">
-        <is>
-          <t>تاريخ المراجعة</t>
         </is>
       </c>
     </row>
@@ -3636,46 +3381,31 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:E1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>الكود</t>
         </is>
       </c>
-      <c r="B1" s="4" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>Task ID</t>
         </is>
       </c>
-      <c r="C1" s="4" t="inlineStr">
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>الفجوة</t>
         </is>
       </c>
-      <c r="D1" s="4" t="inlineStr">
-        <is>
-          <t>الخطورة</t>
-        </is>
-      </c>
-      <c r="E1" s="4" t="inlineStr">
+      <c r="D1" s="3" t="inlineStr">
         <is>
           <t>الإجراء</t>
         </is>
       </c>
-      <c r="F1" s="4" t="inlineStr">
-        <is>
-          <t>المسؤول</t>
-        </is>
-      </c>
-      <c r="G1" s="4" t="inlineStr">
-        <is>
-          <t>الموعد</t>
-        </is>
-      </c>
-      <c r="H1" s="4" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>الحالة</t>
         </is>
@@ -3692,36 +3422,26 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:D1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>التاريخ</t>
         </is>
       </c>
-      <c r="B1" s="4" t="inlineStr">
-        <is>
-          <t>النوع</t>
-        </is>
-      </c>
-      <c r="C1" s="4" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>القرارات</t>
         </is>
       </c>
-      <c r="D1" s="4" t="inlineStr">
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>المسؤول</t>
         </is>
       </c>
-      <c r="E1" s="4" t="inlineStr">
-        <is>
-          <t>الموعد</t>
-        </is>
-      </c>
-      <c r="F1" s="4" t="inlineStr">
+      <c r="D1" s="3" t="inlineStr">
         <is>
           <t>الحالة</t>
         </is>
@@ -3738,28 +3458,91 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D1"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>الكود</t>
         </is>
       </c>
-      <c r="B1" s="4" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>الاسم</t>
         </is>
       </c>
-      <c r="C1" s="4" t="inlineStr">
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>الدور</t>
         </is>
       </c>
-      <c r="D1" s="4" t="inlineStr">
-        <is>
-          <t>عدد المهام</t>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>عضو فريق P2 رقم 1</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>عضو فريق تصميم البرنامج</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>عضو فريق P2 رقم 2</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>عضو فريق تصميم البرنامج</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>عضو فريق P2 رقم 3</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>عضو فريق تصميم البرنامج</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>P4</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>عضو فريق P2 رقم 4</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>عضو فريق تصميم البرنامج</t>
         </is>
       </c>
     </row>
